--- a/artfynd/A 51492-2024 artfynd.xlsx
+++ b/artfynd/A 51492-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118547599</v>
+        <v>118547608</v>
       </c>
       <c r="B2" t="n">
-        <v>97895</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433837</v>
+        <v>433896</v>
       </c>
       <c r="R2" t="n">
-        <v>6406930</v>
+        <v>6406976</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +775,7 @@
         <v>118547598</v>
       </c>
       <c r="B3" t="n">
-        <v>58107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118547608</v>
+        <v>118547599</v>
       </c>
       <c r="B4" t="n">
-        <v>74417</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>219875</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433896</v>
+        <v>433837</v>
       </c>
       <c r="R4" t="n">
-        <v>6406976</v>
+        <v>6406930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,6 +968,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118547610</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Viken, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>433750</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6406988</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bottnaryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51492-2024 artfynd.xlsx
+++ b/artfynd/A 51492-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118547608</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118547598</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118547599</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,8 +1085,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118547610</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>